--- a/design-data/住宅プランAI_DATABASE.xlsx
+++ b/design-data/住宅プランAI_DATABASE.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="①物件基本情報" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="②家族・要望" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③部屋・面積" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④動線・採光" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤構造・評価" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥図面ファイル" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="①物件基本情報" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="②家族・要望" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="③部屋・面積" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="④動線・採光" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="⑤構造・評価" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="⑥図面ファイル" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="使い方" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'①物件基本情報'!$A$1:$O$501</definedName>
@@ -555,9 +555,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2">
         <f>IF(D2="","",D2/3.305785)</f>
@@ -571,16 +579,26 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
+      <c r="K2" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2">
         <f>IF(D3="","",D3/3.305785)</f>
@@ -601,9 +619,17 @@
       <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2">
         <f>IF(D4="","",D4/3.305785)</f>
@@ -614,19 +640,31 @@
         <f>IF(F4="","",F4/3.305785)</f>
         <v/>
       </c>
-      <c r="H4" s="2" t="n"/>
+      <c r="H4" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
+      <c r="K4" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2">
         <f>IF(D5="","",D5/3.305785)</f>
@@ -637,19 +675,31 @@
         <f>IF(F5="","",F5/3.305785)</f>
         <v/>
       </c>
-      <c r="H5" s="2" t="n"/>
+      <c r="H5" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
+      <c r="K5" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2">
         <f>IF(D6="","",D6/3.305785)</f>
@@ -663,16 +713,26 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
+      <c r="K6" s="2" t="n">
+        <v>4.1</v>
+      </c>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2">
         <f>IF(D7="","",D7/3.305785)</f>
@@ -683,19 +743,33 @@
         <f>IF(F7="","",F7/3.305785)</f>
         <v/>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+      <c r="H7" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>18.6</v>
+      </c>
       <c r="J7" s="2" t="n"/>
-      <c r="K7" s="2" t="n"/>
+      <c r="K7" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
       <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2">
         <f>IF(D8="","",D8/3.305785)</f>
@@ -707,18 +781,30 @@
         <v/>
       </c>
       <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
+      <c r="I8" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
+      <c r="K8" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2">
         <f>IF(D9="","",D9/3.305785)</f>
@@ -730,18 +816,30 @@
         <v/>
       </c>
       <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
+      <c r="I9" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
+      <c r="K9" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
       <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2">
         <f>IF(D10="","",D10/3.305785)</f>
@@ -755,17 +853,29 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
+      <c r="K10" s="2" t="n">
+        <v>6.1</v>
+      </c>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>115.92</v>
+      </c>
       <c r="E11" s="2">
         <f>IF(D11="","",D11/3.305785)</f>
         <v/>
@@ -777,7 +887,11 @@
       </c>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>南</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
@@ -785,9 +899,17 @@
       <c r="O11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2">
         <f>IF(D12="","",D12/3.305785)</f>
@@ -798,10 +920,14 @@
         <f>IF(F12="","",F12/3.305785)</f>
         <v/>
       </c>
-      <c r="H12" s="2" t="n"/>
+      <c r="H12" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+      <c r="K12" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
@@ -24403,23 +24529,49 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="D2" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>5.2</v>
+      </c>
       <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
+      <c r="H2" s="2" t="n">
+        <v>4.5</v>
+      </c>
       <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
+      <c r="J2" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="2">
@@ -24428,23 +24580,49 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="D3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>5.2</v>
+      </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
+      <c r="I3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
+      <c r="L3" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
       <c r="T3" s="2">
@@ -24453,23 +24631,45 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>17.6</v>
+      </c>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="D4" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
       <c r="T4" s="2">
@@ -24478,23 +24678,47 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>17.3</v>
+      </c>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="D5" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
+      <c r="L5" s="2" t="n">
+        <v>2.6</v>
+      </c>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="2">
@@ -24503,23 +24727,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>17.3</v>
+      </c>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="D6" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
+      <c r="J6" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
+      <c r="L6" s="2" t="n">
+        <v>2.6</v>
+      </c>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="2">
@@ -24528,23 +24776,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="D7" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>5.3</v>
+      </c>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="2">
@@ -24553,23 +24825,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="D8" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>5.3</v>
+      </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
+      <c r="L8" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="2">
@@ -24578,23 +24874,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>5.2</v>
+      </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
+      <c r="J9" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="2">
@@ -24603,12 +24921,24 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>5.2</v>
+      </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
@@ -24628,23 +24958,55 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>4.5</v>
+      </c>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
+      <c r="K11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1.0坪</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="2">
@@ -24653,21 +25015,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
+      <c r="I12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
+      <c r="L12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1.25坪</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="n"/>
       <c r="Q12" s="2" t="n"/>
       <c r="R12" s="2" t="n"/>
@@ -47742,8 +48130,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>木造軸組</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
@@ -61743,15 +62139,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T501"/>
-  <conditionalFormatting sqref="O2:O501">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="60"/>
-        <cfvo type="num" val="80"/>
-        <cfvo type="num" val="100"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="12">
     <dataValidation sqref="B2:B501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"木造軸組,2×4,2×6,その他"</formula1>
@@ -61862,114 +62249,202 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>出典: daimaru-fudosan.com 分譲住宅 販売図面(他社物件)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>出典: daimaru-fudosan.com 分譲住宅 販売図面(他社物件)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>出典: daimaru-fudosan.com 分譲住宅 販売図面(他社物件)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>出典: daimaru-fudosan.com 分譲住宅 販売図面(他社物件)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>出典: daimaru-fudosan.com 分譲住宅 販売図面(他社物件)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>出典: daimaru-fudosan.com 分譲住宅 販売図面(他社物件)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>出典: daimaru-fudosan.com 分譲住宅 販売図面(他社物件)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>出典: daimaru-fudosan.com 分譲住宅 販売図面(他社物件)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>出典: daimaru-fudosan.com 分譲住宅 販売図面(他社物件)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>出典: 出所不明の規格プラン資料(他社の可能性あり・要確認)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>出典: 出所不明の規格プラン資料(他社の可能性あり・要確認)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>

--- a/design-data/住宅プランAI_DATABASE.xlsx
+++ b/design-data/住宅プランAI_DATABASE.xlsx
@@ -934,10 +934,20 @@
       <c r="O12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
       <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2階</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>120.86</v>
+      </c>
       <c r="E13" s="2">
         <f>IF(D13="","",D13/3.305785)</f>
         <v/>
@@ -25066,14 +25076,28 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>18</v>
+      </c>
       <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5.23</v>
+      </c>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="H13" s="2" t="n">
+        <v>4.5</v>
+      </c>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
@@ -25081,8 +25105,16 @@
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="2">
@@ -48166,7 +48198,11 @@
       <c r="T2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
@@ -48185,7 +48221,9 @@
         <v/>
       </c>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n">
+        <v>1200.06</v>
+      </c>
       <c r="R3" s="2">
         <f>IFERROR(Q3/VLOOKUP(A3,'①物件基本情報'!$A:$E,5,FALSE),"")</f>
         <v/>

--- a/design-data/住宅プランAI_DATABASE.xlsx
+++ b/design-data/住宅プランAI_DATABASE.xlsx
@@ -62485,14 +62485,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>材料費値上げ見込み 8%(建物本体 12,960,689円・外構 1,050,351円・坪単価 35.4万円 相当)。登録している建物価格は上昇前の金額。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
